--- a/Stats Sheet/Round Gaps/Party of One.xlsx
+++ b/Stats Sheet/Round Gaps/Party of One.xlsx
@@ -517,7 +517,7 @@
     <x:t>Ullti</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
+    <x:t>Nikikula</x:t>
   </x:si>
 </x:sst>
 </file>
